--- a/dal-excel/examples/013.xccy_script_calibration.xlsx
+++ b/dal-excel/examples/013.xccy_script_calibration.xlsx
@@ -18,9 +18,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="166" formatCode="0.000E+00"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -89,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -98,6 +99,18 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
@@ -495,7 +508,7 @@
     <col width="14" customWidth="1" min="24" max="24"/>
     <col width="17" customWidth="1" min="25" max="25"/>
     <col width="13" customWidth="1" min="26" max="26"/>
-    <col width="83" customWidth="1" min="27" max="27"/>
+    <col width="60" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -617,7 +630,7 @@
         </is>
       </c>
       <c r="AA2" s="4">
-        <f>SCRIPTINSTRUMENTDEFINITION.NEW($A$2:$C$11,$E$2:$F$12,$H$2:$P$4,$S$2:$Y$4,)</f>
+        <f>SCRIPTINSTRUMENTDEFINITION.NEW($A$2:$C$11,$E$3:$F$12,$H$2:$P$4,$S$2:$Y$4,)</f>
         <v/>
       </c>
     </row>
@@ -1032,10 +1045,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:V53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="66" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -1044,6 +1057,19 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1121,10 +1147,9 @@
           <t>OIS</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>$F$4</t>
-        </is>
+      <c r="I5" s="5">
+        <f>$F$4</f>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -1194,10 +1219,9 @@
           <t>QUARTERLY</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>$F$4</t>
-        </is>
+      <c r="I9" s="5">
+        <f>$F$4</f>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -1258,10 +1282,9 @@
           <t>OIS</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>$F$5</t>
-        </is>
+      <c r="I13" s="5">
+        <f>$F$5</f>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -1271,7 +1294,7 @@
         </is>
       </c>
       <c r="F14" s="4">
-        <f>XCCYSCRIPTCONTEXT.NEW($H$20:$I$25)</f>
+        <f>XCCYSCRIPTCONTEXT.NEW($H$21:$I$25)</f>
         <v/>
       </c>
     </row>
@@ -1314,7 +1337,7 @@
         </is>
       </c>
       <c r="F17" s="4">
-        <f>CURVEINSTRUMENTCALIBRATIONOPTIONS.NEW($H$28:$I$32)</f>
+        <f>CURVEINSTRUMENTCALIBRATIONOPTIONS.NEW($H$29:$I$32)</f>
         <v/>
       </c>
       <c r="H17" s="5" t="inlineStr">
@@ -1322,10 +1345,9 @@
           <t>SEMIANNUAL</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>$F$5</t>
-        </is>
+      <c r="I17" s="5">
+        <f>$F$5</f>
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -1335,7 +1357,7 @@
         </is>
       </c>
       <c r="F18" s="4">
-        <f>XCCYINSTRUMENTCALIBRATIONSPEC.NEW($H$35:$I$41)</f>
+        <f>XCCYINSTRUMENTCALIBRATIONSPEC.NEW($H$36:$I$41)</f>
         <v/>
       </c>
     </row>
@@ -1405,10 +1427,9 @@
           <t>pair</t>
         </is>
       </c>
-      <c r="I22" s="5" t="inlineStr">
-        <is>
-          <t>$F$12</t>
-        </is>
+      <c r="I22" s="5">
+        <f>$F$12</f>
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -1441,25 +1462,14 @@
           <t>fixings</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>$F$13</t>
-        </is>
+      <c r="I25" s="5">
+        <f>$F$13</f>
+        <v/>
       </c>
     </row>
     <row r="26"/>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>Observation report</t>
-        </is>
-      </c>
-    </row>
+    <row r="27"/>
     <row r="28">
-      <c r="A28" s="4">
-        <f>CALIBRATIONREPORT.GET.OBSERVATIONS($F$21)</f>
-        <v/>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
           <t>field</t>
@@ -1506,11 +1516,6 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>Fitted basis forward</t>
-        </is>
-      </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
           <t>compute_quote_jacobian</t>
@@ -1520,12 +1525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="4">
-        <f>CALIBRATIONREPORT.GET.PARAMETERS($F$21)</f>
-        <v/>
-      </c>
-    </row>
+    <row r="33"/>
     <row r="34"/>
     <row r="35">
       <c r="H35" s="2" t="inlineStr">
@@ -1545,10 +1545,9 @@
           <t>context</t>
         </is>
       </c>
-      <c r="I36" s="5" t="inlineStr">
-        <is>
-          <t>$F$14</t>
-        </is>
+      <c r="I36" s="5">
+        <f>$F$14</f>
+        <v/>
       </c>
     </row>
     <row r="37">
@@ -1557,10 +1556,9 @@
           <t>domestic_curve_block</t>
         </is>
       </c>
-      <c r="I37" s="5" t="inlineStr">
-        <is>
-          <t>$F$8</t>
-        </is>
+      <c r="I37" s="5">
+        <f>$F$8</f>
+        <v/>
       </c>
     </row>
     <row r="38">
@@ -1569,10 +1567,9 @@
           <t>foreign_curve_block</t>
         </is>
       </c>
-      <c r="I38" s="5" t="inlineStr">
-        <is>
-          <t>$F$11</t>
-        </is>
+      <c r="I38" s="5">
+        <f>$F$11</f>
+        <v/>
       </c>
     </row>
     <row r="39">
@@ -1591,10 +1588,9 @@
           <t>knot_dates</t>
         </is>
       </c>
-      <c r="I40" s="5" t="inlineStr">
-        <is>
-          <t>$F$15</t>
-        </is>
+      <c r="I40" s="5">
+        <f>$F$15</f>
+        <v/>
       </c>
     </row>
     <row r="41">
@@ -1603,11 +1599,106 @@
           <t>observations</t>
         </is>
       </c>
-      <c r="I41" s="5" t="inlineStr">
-        <is>
-          <t>$F$16</t>
-        </is>
-      </c>
+      <c r="I41" s="5">
+        <f>$F$16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>Observation report</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="32" customHeight="1">
+      <c r="A46" s="8">
+        <f t="array" ref="A46:V47">CALIBRATIONREPORT.GET.OBSERVATIONS($F$21)</f>
+        <v/>
+      </c>
+      <c r="B46" s="8" t="n"/>
+      <c r="C46" s="8" t="n"/>
+      <c r="D46" s="8" t="n"/>
+      <c r="E46" s="8" t="n"/>
+      <c r="F46" s="8" t="n"/>
+      <c r="G46" s="8" t="n"/>
+      <c r="H46" s="8" t="n"/>
+      <c r="I46" s="8" t="n"/>
+      <c r="J46" s="8" t="n"/>
+      <c r="K46" s="8" t="n"/>
+      <c r="L46" s="9" t="n"/>
+      <c r="M46" s="8" t="n"/>
+      <c r="N46" s="9" t="n"/>
+      <c r="O46" s="9" t="n"/>
+      <c r="P46" s="8" t="n"/>
+      <c r="Q46" s="8" t="n"/>
+      <c r="R46" s="8" t="n"/>
+      <c r="S46" s="8" t="n"/>
+      <c r="T46" s="8" t="n"/>
+      <c r="U46" s="8" t="n"/>
+      <c r="V46" s="8" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="n"/>
+      <c r="B47" s="10" t="n"/>
+      <c r="C47" s="10" t="n"/>
+      <c r="D47" s="10" t="n"/>
+      <c r="E47" s="10" t="n"/>
+      <c r="F47" s="10" t="n"/>
+      <c r="G47" s="10" t="n"/>
+      <c r="H47" s="10" t="n"/>
+      <c r="I47" s="10" t="n"/>
+      <c r="J47" s="10" t="n"/>
+      <c r="K47" s="10" t="n"/>
+      <c r="L47" s="11" t="n"/>
+      <c r="M47" s="10" t="n"/>
+      <c r="N47" s="11" t="n"/>
+      <c r="O47" s="11" t="n"/>
+      <c r="P47" s="10" t="n"/>
+      <c r="Q47" s="10" t="n"/>
+      <c r="R47" s="10" t="n"/>
+      <c r="S47" s="10" t="n"/>
+      <c r="T47" s="10" t="n"/>
+      <c r="U47" s="10" t="n"/>
+      <c r="V47" s="10" t="n"/>
+    </row>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>Fitted parameters</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="32" customHeight="1">
+      <c r="A52" s="8">
+        <f t="array" ref="A52:I53">CALIBRATIONREPORT.GET.PARAMETERS($F$21)</f>
+        <v/>
+      </c>
+      <c r="B52" s="8" t="n"/>
+      <c r="C52" s="8" t="n"/>
+      <c r="D52" s="8" t="n"/>
+      <c r="E52" s="8" t="n"/>
+      <c r="F52" s="8" t="n"/>
+      <c r="G52" s="8" t="n"/>
+      <c r="H52" s="8" t="n"/>
+      <c r="I52" s="8" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="10" t="n"/>
+      <c r="B53" s="10" t="n"/>
+      <c r="C53" s="10" t="n"/>
+      <c r="D53" s="10" t="n"/>
+      <c r="E53" s="10" t="n"/>
+      <c r="F53" s="10" t="n"/>
+      <c r="G53" s="10" t="n"/>
+      <c r="H53" s="10" t="n"/>
+      <c r="I53" s="10" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1623,7 +1714,7 @@
   <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="115" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -1648,42 +1739,42 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>The Script Instrument sheet contains the complete direct source definition: two USD 3M coupons, one EUR 6M spread coupon, and initial/final principal exchanges with FX conversion.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>N=110 USD, foreign/domestic notional ratio=100/110, K=0.001, spread on the foreign leg, explicit USD.OIS collateral, and signed BasisSpread measure with annuity sign -1 and floor 1e-12.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>The calibration uses USD 4% and EUR 2% piecewise-constant forward curves, FX spot 1.1, one basis knot at 2027-11-04, and the original quote -0.002983490837363863.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>The default XCCY solver initial guess is 0. The basis parameterization is PIECEWISE_CONSTANT_FWD. Options select AAD and the quote Jacobian.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Run INIT.GLOBALDATA(1), then recalculate. The expected basis forward is 0.003 and the outcome status is Succeeded.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>This file contains formulas, not cached results; generating it does not execute Excel.</t>
         </is>
